--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_item/lang_item__name_title__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_item/lang_item__name_title__part_0001.xlsx
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Audio Casket</t>
+          <t>Hộp Âm Thanh</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Exile Weapon</t>
+          <t>Exile Vũ khí</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>EXP material for weapon</t>
+          <t>EXP material for vũ khí</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Breakthrough Material for weapon</t>
+          <t>Breakthrough Material for vũ khí</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
